--- a/outputs/Block5B_Senate_2026_Fold_Races.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Races.xlsx
@@ -474,10 +474,10 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>1.119500130174437</v>
+        <v>3.498315625809795</v>
       </c>
       <c r="E2">
-        <v>-3.635116607323695</v>
+        <v>-7.176472161128217</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -497,13 +497,13 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>7.750472589792061</v>
+        <v>8.458498023715421</v>
       </c>
       <c r="E3">
-        <v>3.00818729023427</v>
+        <v>-1.695802107663628</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -520,10 +520,10 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>2.006045616927736</v>
+        <v>3.203230148048448</v>
       </c>
       <c r="E4">
-        <v>-1.895149067445937</v>
+        <v>-6.995912889582467</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -543,10 +543,10 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>6.077348066298342</v>
+        <v>8.232189973614787</v>
       </c>
       <c r="E5">
-        <v>5.399343135599748</v>
+        <v>0.383899469915236</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
@@ -566,10 +566,10 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>2.231447846393365</v>
+        <v>1.750772399588051</v>
       </c>
       <c r="E6">
-        <v>-2.050073786536359</v>
+        <v>-9.075435312273683</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -589,10 +589,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>-0.8942661756970125</v>
+        <v>1.856335754640838</v>
       </c>
       <c r="E7">
-        <v>-6.301021246078991</v>
+        <v>-11.11754838992667</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -612,10 +612,10 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>-0.9895833333333286</v>
+        <v>1.497081958893681</v>
       </c>
       <c r="E8">
-        <v>-5.883831807819039</v>
+        <v>-8.655528146621872</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -638,10 +638,10 @@
         <v>6.065400843881861</v>
       </c>
       <c r="E9">
-        <v>5.266836508724185</v>
+        <v>-2.348561440178459</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
@@ -658,10 +658,10 @@
         <v>18</v>
       </c>
       <c r="D10">
-        <v>-1.396070320579113</v>
+        <v>-2.410596026490069</v>
       </c>
       <c r="E10">
-        <v>-5.85181516740011</v>
+        <v>-14.69916668017758</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -681,10 +681,10 @@
         <v>18</v>
       </c>
       <c r="D11">
-        <v>-10.40000000000001</v>
+        <v>-7.215793060150304</v>
       </c>
       <c r="E11">
-        <v>-11.50553911162613</v>
+        <v>-16.77952132936703</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -704,10 +704,10 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>-11.59999999999999</v>
+        <v>-21.88581315216757</v>
       </c>
       <c r="E12">
-        <v>-12.48832004491035</v>
+        <v>-39.67221627274333</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -727,10 +727,10 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>1.119500130174437</v>
+        <v>3.498315625809795</v>
       </c>
       <c r="E13">
-        <v>1.119500130174437</v>
+        <v>3.498315625809795</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -750,10 +750,10 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>7.750472589792061</v>
+        <v>8.458498023715421</v>
       </c>
       <c r="E14">
-        <v>7.750472589792061</v>
+        <v>8.458498023715421</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -773,10 +773,10 @@
         <v>19</v>
       </c>
       <c r="D15">
-        <v>2.006045616927736</v>
+        <v>3.203230148048448</v>
       </c>
       <c r="E15">
-        <v>2.006045616927736</v>
+        <v>3.203230148048448</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
@@ -796,10 +796,10 @@
         <v>19</v>
       </c>
       <c r="D16">
-        <v>6.077348066298342</v>
+        <v>8.232189973614787</v>
       </c>
       <c r="E16">
-        <v>6.077348066298342</v>
+        <v>8.232189973614787</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -819,10 +819,10 @@
         <v>18</v>
       </c>
       <c r="D17">
-        <v>2.231447846393365</v>
+        <v>1.750772399588051</v>
       </c>
       <c r="E17">
-        <v>2.231447846393365</v>
+        <v>1.750772399588051</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -842,13 +842,13 @@
         <v>18</v>
       </c>
       <c r="D18">
-        <v>-0.8942661756970125</v>
+        <v>1.856335754640838</v>
       </c>
       <c r="E18">
-        <v>-0.8942661756970125</v>
+        <v>1.856335754640838</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
         <v>20</v>
@@ -865,13 +865,13 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>-0.9895833333333286</v>
+        <v>1.497081958893681</v>
       </c>
       <c r="E19">
-        <v>-0.9895833333333286</v>
+        <v>1.497081958893681</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
         <v>20</v>
@@ -911,10 +911,10 @@
         <v>18</v>
       </c>
       <c r="D21">
-        <v>-1.396070320579113</v>
+        <v>-2.410596026490069</v>
       </c>
       <c r="E21">
-        <v>-1.396070320579113</v>
+        <v>-2.410596026490069</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -934,10 +934,10 @@
         <v>18</v>
       </c>
       <c r="D22">
-        <v>-10.40000000000001</v>
+        <v>-7.215793060150304</v>
       </c>
       <c r="E22">
-        <v>-10.40000000000001</v>
+        <v>-7.215793060150304</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -957,10 +957,10 @@
         <v>18</v>
       </c>
       <c r="D23">
-        <v>-11.59999999999999</v>
+        <v>-21.88581315216757</v>
       </c>
       <c r="E23">
-        <v>-11.59999999999999</v>
+        <v>-21.88581315216757</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -980,13 +980,13 @@
         <v>18</v>
       </c>
       <c r="D24">
-        <v>1.119500130174437</v>
+        <v>3.498315625809795</v>
       </c>
       <c r="E24">
-        <v>-0.530352993283286</v>
+        <v>2.650647024781429</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
         <v>21</v>
@@ -1003,10 +1003,10 @@
         <v>18</v>
       </c>
       <c r="D25">
-        <v>7.750472589792061</v>
+        <v>8.458498023715421</v>
       </c>
       <c r="E25">
-        <v>5.473371609970776</v>
+        <v>7.738543123737648</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -1026,10 +1026,10 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>2.006045616927736</v>
+        <v>3.203230148048448</v>
       </c>
       <c r="E26">
-        <v>2.40808133434199</v>
+        <v>5.027582767314211</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
@@ -1049,10 +1049,10 @@
         <v>19</v>
       </c>
       <c r="D27">
-        <v>6.077348066298342</v>
+        <v>8.232189973614787</v>
       </c>
       <c r="E27">
-        <v>9.848596397380661</v>
+        <v>12.31460748976793</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -1072,10 +1072,10 @@
         <v>18</v>
       </c>
       <c r="D28">
-        <v>2.231447846393365</v>
+        <v>1.750772399588051</v>
       </c>
       <c r="E28">
-        <v>1.026350111420086</v>
+        <v>0.8954172418715476</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -1095,10 +1095,10 @@
         <v>18</v>
       </c>
       <c r="D29">
-        <v>-0.8942661756970125</v>
+        <v>1.856335754640838</v>
       </c>
       <c r="E29">
-        <v>-3.136880672666528</v>
+        <v>-1.516711512570621</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -1118,13 +1118,13 @@
         <v>18</v>
       </c>
       <c r="D30">
-        <v>-0.9895833333333286</v>
+        <v>1.497081958893681</v>
       </c>
       <c r="E30">
-        <v>-2.627403489415104</v>
+        <v>1.452720731242803</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
         <v>21</v>
@@ -1164,10 +1164,10 @@
         <v>18</v>
       </c>
       <c r="D32">
-        <v>-1.396070320579113</v>
+        <v>-2.410596026490069</v>
       </c>
       <c r="E32">
-        <v>-2.494514232879649</v>
+        <v>-4.641341142383808</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -1187,10 +1187,10 @@
         <v>18</v>
       </c>
       <c r="D33">
-        <v>-10.40000000000001</v>
+        <v>-7.215793060150304</v>
       </c>
       <c r="E33">
-        <v>-6.979829876754016</v>
+        <v>-5.941181113156134</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -1210,10 +1210,10 @@
         <v>18</v>
       </c>
       <c r="D34">
-        <v>-11.59999999999999</v>
+        <v>-21.88581315216757</v>
       </c>
       <c r="E34">
-        <v>-7.845302386032147</v>
+        <v>-29.22220350797864</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -1233,13 +1233,13 @@
         <v>18</v>
       </c>
       <c r="D35">
-        <v>1.119500130174437</v>
+        <v>3.498315625809795</v>
       </c>
       <c r="E35">
-        <v>-7.991268636298971</v>
+        <v>2.032823649239744</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35" t="s">
         <v>20</v>
@@ -1256,13 +1256,13 @@
         <v>18</v>
       </c>
       <c r="D36">
-        <v>7.750472589792061</v>
+        <v>8.458498023715421</v>
       </c>
       <c r="E36">
-        <v>-1.977759998573099</v>
+        <v>6.943821333383879</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
         <v>20</v>
@@ -1279,13 +1279,13 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>2.006045616927736</v>
+        <v>3.203230148048448</v>
       </c>
       <c r="E37">
-        <v>-6.772500854639566</v>
+        <v>3.313391651156564</v>
       </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G37" t="s">
         <v>20</v>
@@ -1302,13 +1302,13 @@
         <v>19</v>
       </c>
       <c r="D38">
-        <v>6.077348066298342</v>
+        <v>8.232189973614787</v>
       </c>
       <c r="E38">
-        <v>-0.4846225547925229</v>
+        <v>9.764152809749833</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
         <v>20</v>
@@ -1325,13 +1325,13 @@
         <v>18</v>
       </c>
       <c r="D39">
-        <v>2.231447846393365</v>
+        <v>1.750772399588051</v>
       </c>
       <c r="E39">
-        <v>-6.602644263031961</v>
+        <v>0.328403642916468</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39" t="s">
         <v>20</v>
@@ -1348,10 +1348,10 @@
         <v>18</v>
       </c>
       <c r="D40">
-        <v>-0.8942661756970125</v>
+        <v>1.856335754640838</v>
       </c>
       <c r="E40">
-        <v>-10.38858325292123</v>
+        <v>-1.309652956723542</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -1371,13 +1371,13 @@
         <v>18</v>
       </c>
       <c r="D41">
-        <v>-0.9895833333333286</v>
+        <v>1.497081958893681</v>
       </c>
       <c r="E41">
-        <v>-10.06626130089964</v>
+        <v>0.6424537334128565</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>6.065400843881861</v>
       </c>
       <c r="E42">
-        <v>-0.5927564181068075</v>
+        <v>7.345766304429231</v>
       </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
         <v>20</v>
@@ -1417,10 +1417,10 @@
         <v>18</v>
       </c>
       <c r="D43">
-        <v>-1.396070320579113</v>
+        <v>-2.410596026490069</v>
       </c>
       <c r="E43">
-        <v>-10.10199173231504</v>
+        <v>-4.748170664481129</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -1440,10 +1440,10 @@
         <v>18</v>
       </c>
       <c r="D44">
-        <v>-10.40000000000001</v>
+        <v>-7.215793060150304</v>
       </c>
       <c r="E44">
-        <v>-16.02966504416926</v>
+        <v>-7.155350779947925</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -1463,10 +1463,10 @@
         <v>18</v>
       </c>
       <c r="D45">
-        <v>-11.59999999999999</v>
+        <v>-21.88581315216757</v>
       </c>
       <c r="E45">
-        <v>-17.00475432417813</v>
+        <v>-27.85683953776087</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -1486,13 +1486,13 @@
         <v>18</v>
       </c>
       <c r="D46">
-        <v>1.119500130174437</v>
+        <v>3.498315625809795</v>
       </c>
       <c r="E46">
-        <v>-2.827852922905387</v>
+        <v>0.6033611172084861</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
         <v>21</v>
@@ -1509,10 +1509,10 @@
         <v>18</v>
       </c>
       <c r="D47">
-        <v>7.750472589792061</v>
+        <v>8.458498023715421</v>
       </c>
       <c r="E47">
-        <v>4.337089984632125</v>
+        <v>6.46321041296996</v>
       </c>
       <c r="F47" t="s">
         <v>19</v>
@@ -1532,13 +1532,13 @@
         <v>19</v>
       </c>
       <c r="D48">
-        <v>2.006045616927736</v>
+        <v>3.203230148048448</v>
       </c>
       <c r="E48">
-        <v>-0.1672601165464371</v>
+        <v>2.413194676107785</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48" t="s">
         <v>21</v>
@@ -1555,10 +1555,10 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>6.077348066298342</v>
+        <v>8.232189973614787</v>
       </c>
       <c r="E49">
-        <v>7.378175573810604</v>
+        <v>10.13813397597216</v>
       </c>
       <c r="F49" t="s">
         <v>19</v>
@@ -1578,10 +1578,10 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>2.231447846393365</v>
+        <v>1.750772399588051</v>
       </c>
       <c r="E50">
-        <v>-1.165492557175527</v>
+        <v>-1.429881313643518</v>
       </c>
       <c r="F50" t="s">
         <v>18</v>
@@ -1601,10 +1601,10 @@
         <v>18</v>
       </c>
       <c r="D51">
-        <v>-0.8942661756970125</v>
+        <v>1.856335754640838</v>
       </c>
       <c r="E51">
-        <v>-5.491928930119531</v>
+        <v>-3.417378482927037</v>
       </c>
       <c r="F51" t="s">
         <v>18</v>
@@ -1624,10 +1624,10 @@
         <v>18</v>
       </c>
       <c r="D52">
-        <v>-0.9895833333333286</v>
+        <v>1.497081958893681</v>
       </c>
       <c r="E52">
-        <v>-5.077702110704545</v>
+        <v>-1.044465232996661</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -1670,10 +1670,10 @@
         <v>18</v>
       </c>
       <c r="D54">
-        <v>-1.396070320579113</v>
+        <v>-2.410596026490069</v>
       </c>
       <c r="E54">
-        <v>-5.020649128521597</v>
+        <v>-6.955336546975865</v>
       </c>
       <c r="F54" t="s">
         <v>18</v>
@@ -1693,10 +1693,10 @@
         <v>18</v>
       </c>
       <c r="D55">
-        <v>-10.40000000000001</v>
+        <v>-7.215793060150304</v>
       </c>
       <c r="E55">
-        <v>-9.982608649878454</v>
+        <v>-8.686713221810152</v>
       </c>
       <c r="F55" t="s">
         <v>18</v>
@@ -1716,10 +1716,10 @@
         <v>18</v>
       </c>
       <c r="D56">
-        <v>-11.59999999999999</v>
+        <v>-21.88581315216757</v>
       </c>
       <c r="E56">
-        <v>-10.86825093902745</v>
+        <v>-30.15733572493856</v>
       </c>
       <c r="F56" t="s">
         <v>18</v>
